--- a/lab1/lab1.xlsx
+++ b/lab1/lab1.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>МИН</t>
   </si>
@@ -204,7 +204,7 @@
 четвертого порядка</t>
   </si>
   <si>
-    <t>третьего порядка</t>
+    <t xml:space="preserve">Коэффициент асимметрии </t>
   </si>
   <si>
     <t>Коэфициент экцесса</t>
@@ -214,6 +214,30 @@
   </si>
   <si>
     <t>m</t>
+  </si>
+  <si>
+    <t>Показатель</t>
+  </si>
+  <si>
+    <t>Исходные данные</t>
+  </si>
+  <si>
+    <t>Интервальный ряд</t>
+  </si>
+  <si>
+    <t>Ошибка σ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент асимметрии As </t>
+  </si>
+  <si>
+    <t>|As|/σAs</t>
+  </si>
+  <si>
+    <t>Коэффициент эксцесса Ex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|Ex|/σEx </t>
   </si>
   <si>
     <t>w нак</t>
@@ -231,7 +255,7 @@
     <numFmt numFmtId="180" formatCode="0.0000"/>
     <numFmt numFmtId="181" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,13 +268,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -731,28 +748,31 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -761,123 +781,120 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -901,15 +918,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -5417,7 +5428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP57"/>
+  <dimension ref="A1:AU57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="10" width="5" customWidth="1"/>
@@ -5441,6 +5452,10 @@
     <col min="40" max="40" width="11.5625" customWidth="1"/>
     <col min="41" max="41" width="10.015625" customWidth="1"/>
     <col min="42" max="42" width="17.015625" customWidth="1"/>
+    <col min="44" max="44" width="25.9375" customWidth="1"/>
+    <col min="45" max="45" width="17.125" customWidth="1"/>
+    <col min="46" max="46" width="17.875" customWidth="1"/>
+    <col min="47" max="47" width="9.5625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -6156,7 +6171,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1" spans="11:42">
+    <row r="19" ht="19" customHeight="1" spans="11:47">
       <c r="AB19" s="9" t="s">
         <v>15</v>
       </c>
@@ -6187,7 +6202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="11:42">
+    <row r="20" spans="11:47">
       <c r="K20" t="str">
         <f>TEXT(S2,"0,00")&amp;"–"&amp;TEXT(T2,"0,00")</f>
         <v>ai–bi</v>
@@ -6212,15 +6227,15 @@
         <v>5.4717</v>
       </c>
       <c r="AM20" s="9"/>
-      <c r="AN20" s="12" t="s">
+      <c r="AN20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AO20" s="12" t="s">
+      <c r="AO20" s="9" t="s">
         <v>21</v>
       </c>
       <c r="AP20" s="9"/>
     </row>
-    <row r="21" spans="11:42">
+    <row r="21" spans="11:47">
       <c r="K21" t="str">
         <f t="shared" ref="K21:K28" si="6">TEXT(S3,"0,00")&amp;"–"&amp;TEXT(T3,"0,00")</f>
         <v>4,98–5,09</v>
@@ -6249,7 +6264,7 @@
       <c r="AO21" s="10"/>
       <c r="AP21" s="10"/>
     </row>
-    <row r="22" spans="11:42">
+    <row r="22" spans="11:47">
       <c r="K22" t="str">
         <f t="shared" si="6"/>
         <v>5,09–5,20</v>
@@ -6281,20 +6296,20 @@
       <c r="AM22" t="s">
         <v>28</v>
       </c>
-      <c r="AN22" s="13">
+      <c r="AN22" s="12">
         <f>AI25</f>
         <v>0.02821251</v>
       </c>
-      <c r="AO22" s="13">
+      <c r="AO22" s="12">
         <f>_xlfn.VAR.P(X)</f>
         <v>0.02821251</v>
       </c>
-      <c r="AP22" s="13">
+      <c r="AP22" s="12">
         <f>AJ25</f>
         <v>0.0286661100000002</v>
       </c>
     </row>
-    <row r="23" ht="34" spans="11:42">
+    <row r="23" ht="34" spans="11:47">
       <c r="K23" t="str">
         <f t="shared" si="6"/>
         <v>5,20–5,31</v>
@@ -6305,7 +6320,7 @@
       <c r="AC23">
         <v>5.4441</v>
       </c>
-      <c r="AD23" s="14">
+      <c r="AD23" s="13">
         <f>HARMEAN(X)</f>
         <v>5.44410601929593</v>
       </c>
@@ -6323,20 +6338,20 @@
         <f t="array" ref="AJ23">SUMPRODUCT(V3:V10,U3:U10^4)/100</f>
         <v>901.509874777726</v>
       </c>
-      <c r="AM23" s="15" t="s">
+      <c r="AM23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AN23" s="13">
+      <c r="AN23" s="12">
         <f>SQRT(AN22)</f>
         <v>0.167965800090376</v>
       </c>
-      <c r="AO23" s="13"/>
-      <c r="AP23" s="13">
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12">
         <f>SQRT(AP22)</f>
         <v>0.169310690743379</v>
       </c>
     </row>
-    <row r="24" spans="11:42">
+    <row r="24" spans="11:47">
       <c r="K24" t="str">
         <f t="shared" si="6"/>
         <v>5,31–5,42</v>
@@ -6347,7 +6362,7 @@
       <c r="AC24">
         <v>5.4467</v>
       </c>
-      <c r="AD24" s="14">
+      <c r="AD24" s="13">
         <f>GEOMEAN(X)</f>
         <v>5.44670600437583</v>
       </c>
@@ -6357,28 +6372,28 @@
       <c r="AH24" t="s">
         <v>33</v>
       </c>
-      <c r="AI24" s="16" cm="1">
+      <c r="AI24" s="14" cm="1">
         <f t="array" ref="AI24">SUMPRODUCT((X-AVERAGE(X))^1)/100</f>
         <v>7.37188088351104e-16</v>
       </c>
-      <c r="AJ24" s="16" cm="1">
+      <c r="AJ24" s="14" cm="1">
         <f t="array" ref="AJ24">SUMPRODUCT(V3:V10,(U3:U10-SUMPRODUCT(U3:U10,V3:V10)/SUM(V3:V10))^1)/100</f>
         <v>-1.95399252334028e-16</v>
       </c>
       <c r="AM24" t="s">
         <v>34</v>
       </c>
-      <c r="AN24" s="17">
+      <c r="AN24" s="15">
         <f>AN23/AVERAGE(X)*100</f>
         <v>3.0823371825808</v>
       </c>
-      <c r="AO24" s="18"/>
-      <c r="AP24" s="17" cm="1">
+      <c r="AO24" s="16"/>
+      <c r="AP24" s="15" cm="1">
         <f t="array" ref="AP24">AP23/(SUMPRODUCT(U3:U10,V3:V10)/SUM(V3:V10))*100</f>
         <v>3.09429776382804</v>
       </c>
     </row>
-    <row r="25" ht="34" spans="11:42">
+    <row r="25" ht="34" spans="11:47">
       <c r="K25" t="str">
         <f t="shared" si="6"/>
         <v>5,42–5,53</v>
@@ -6403,24 +6418,24 @@
         <f t="array" ref="AI25">SUMPRODUCT((X-AVERAGE(X))^2)/100</f>
         <v>0.02821251</v>
       </c>
-      <c r="AJ25" s="16" cm="1">
+      <c r="AJ25" s="14" cm="1">
         <f t="array" ref="AJ25">SUMPRODUCT(V3:V10,(U3:U10-SUMPRODUCT(U3:U10,V3:V10)/SUM(V3:V10))^2)/100</f>
         <v>0.0286661100000002</v>
       </c>
-      <c r="AM25" s="15" t="s">
+      <c r="AM25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AN25" s="19">
+      <c r="AN25" s="17">
         <f>AI24</f>
         <v>7.37188088351104e-16</v>
       </c>
-      <c r="AO25" s="13"/>
-      <c r="AP25" s="19">
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="17">
         <f>AJ24</f>
         <v>-1.95399252334028e-16</v>
       </c>
     </row>
-    <row r="26" ht="34" spans="11:42">
+    <row r="26" ht="34" spans="11:47">
       <c r="K26" t="str">
         <f t="shared" si="6"/>
         <v>5,53–5,64</v>
@@ -6445,24 +6460,24 @@
         <f t="array" ref="AI26">SUMPRODUCT((X-AVERAGE(X))^3)/100</f>
         <v>-0.000203263385999937</v>
       </c>
-      <c r="AJ26" s="16" cm="1">
+      <c r="AJ26" s="14" cm="1">
         <f t="array" ref="AJ26">SUMPRODUCT(V3:V10,(U3:U10-SUMPRODUCT(U3:U10,V3:V10)/SUM(V3:V10))^3)/100</f>
         <v>-0.000714419574000022</v>
       </c>
-      <c r="AM26" s="15" t="s">
+      <c r="AM26" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AN26" s="13">
+      <c r="AN26" s="12">
         <f>AI26</f>
         <v>-0.000203263385999937</v>
       </c>
-      <c r="AO26" s="13"/>
-      <c r="AP26" s="13">
+      <c r="AO26" s="12"/>
+      <c r="AP26" s="12">
         <f>AJ25</f>
         <v>0.0286661100000002</v>
       </c>
     </row>
-    <row r="27" ht="34" spans="11:42">
+    <row r="27" ht="34" spans="11:47">
       <c r="K27" t="str">
         <f t="shared" si="6"/>
         <v>5,64–5,75</v>
@@ -6474,76 +6489,76 @@
         <f t="array" ref="AI27">SUMPRODUCT((X-AVERAGE(X))^4)/100</f>
         <v>0.0023744180174997</v>
       </c>
-      <c r="AJ27" s="16" cm="1">
+      <c r="AJ27" s="14" cm="1">
         <f t="array" ref="AJ27">SUMPRODUCT(V3:V10,(U3:U10-SUMPRODUCT(U3:U10,V3:V10)/SUM(V3:V10))^4)/100</f>
         <v>0.00230343859940373</v>
       </c>
-      <c r="AM27" s="15" t="s">
+      <c r="AM27" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AN27" s="13">
+      <c r="AN27" s="12">
         <f>AI27</f>
         <v>0.0023744180174997</v>
       </c>
-      <c r="AO27" s="13"/>
-      <c r="AP27" s="13">
+      <c r="AO27" s="12"/>
+      <c r="AP27" s="12">
         <f>AJ26</f>
         <v>-0.000714419574000022</v>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" spans="11:42">
+    <row r="28" ht="30" customHeight="1" spans="11:47">
       <c r="K28" t="str">
         <f t="shared" si="6"/>
         <v>5,75–5,86</v>
       </c>
-      <c r="AM28" s="20" t="s">
+      <c r="AM28" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="AN28" s="13">
+      <c r="AN28" s="12">
         <f>AI27</f>
         <v>0.0023744180174997</v>
       </c>
-      <c r="AO28" s="13"/>
-      <c r="AP28" s="13">
+      <c r="AO28" s="12"/>
+      <c r="AP28" s="12">
         <f>AJ27</f>
         <v>0.00230343859940373</v>
       </c>
     </row>
-    <row r="29" spans="11:42">
+    <row r="29" spans="11:47">
       <c r="AM29" t="s">
         <v>44</v>
       </c>
-      <c r="AN29" s="13">
+      <c r="AN29" s="12">
         <f>AI26/AN23^3</f>
         <v>-0.0428940019139835</v>
       </c>
-      <c r="AO29" s="13">
+      <c r="AO29" s="12">
         <f>SKEW(X)</f>
         <v>-0.0435499928894295</v>
       </c>
-      <c r="AP29" s="13">
+      <c r="AP29" s="12">
         <f>AJ26/AP23^3</f>
         <v>-0.147197420844705</v>
       </c>
     </row>
-    <row r="30" spans="11:42">
+    <row r="30" spans="11:47">
       <c r="AM30" t="s">
         <v>45</v>
       </c>
-      <c r="AN30" s="13">
+      <c r="AN30" s="12">
         <f>AI27/AN23^4-3</f>
         <v>-0.0168593707522868</v>
       </c>
-      <c r="AO30" s="13">
+      <c r="AO30" s="12">
         <f>KURT((X))</f>
         <v>0.0447531192770798</v>
       </c>
-      <c r="AP30" s="13">
+      <c r="AP30" s="12">
         <f>AJ27/AP23^4-3</f>
         <v>-0.196896626523966</v>
       </c>
     </row>
-    <row r="31" spans="11:42">
+    <row r="31" spans="11:47">
       <c r="K31" t="s">
         <v>46</v>
       </c>
@@ -6551,7 +6566,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="11:42">
+    <row r="32" spans="11:47">
       <c r="K32">
         <f>U3-Q3</f>
         <v>4.925</v>
@@ -6559,8 +6574,20 @@
       <c r="L32">
         <v>0</v>
       </c>
+      <c r="AR32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AS32" t="s">
+        <v>49</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU32" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="33" spans="11:12">
+    <row r="33" spans="11:44">
       <c r="K33">
         <f>U3</f>
         <v>5.035</v>
@@ -6569,8 +6596,11 @@
         <f>V3</f>
         <v>2</v>
       </c>
+      <c r="AR33" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="34" spans="11:12">
+    <row r="34" spans="11:44">
       <c r="K34">
         <f t="shared" ref="K34:L34" si="7">U4</f>
         <v>5.145</v>
@@ -6579,8 +6609,11 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
+      <c r="AR34" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="35" spans="11:12">
+    <row r="35" spans="11:44">
       <c r="K35">
         <f t="shared" ref="K35:L35" si="8">U5</f>
         <v>5.255</v>
@@ -6589,8 +6622,11 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
+      <c r="AR35" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="36" spans="11:12">
+    <row r="36" spans="11:44">
       <c r="K36">
         <f t="shared" ref="K36:L36" si="9">U6</f>
         <v>5.365</v>
@@ -6599,8 +6635,11 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
+      <c r="AR36" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="37" spans="11:12">
+    <row r="37" spans="11:44">
       <c r="K37">
         <f t="shared" ref="K37:L37" si="10">U7</f>
         <v>5.475</v>
@@ -6610,7 +6649,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="11:12">
+    <row r="38" spans="11:44">
       <c r="K38">
         <f t="shared" ref="K38:L38" si="11">U8</f>
         <v>5.585</v>
@@ -6620,7 +6659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="11:12">
+    <row r="39" spans="11:44">
       <c r="K39">
         <f t="shared" ref="K39:L39" si="12">U9</f>
         <v>5.695</v>
@@ -6630,7 +6669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="11:12">
+    <row r="40" spans="11:44">
       <c r="K40">
         <f t="shared" ref="K40:L40" si="13">U10</f>
         <v>5.805</v>
@@ -6640,7 +6679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="11:12">
+    <row r="41" spans="11:44">
       <c r="K41">
         <f>U10+Q3</f>
         <v>5.915</v>
@@ -6649,12 +6688,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="11:12">
+    <row r="48" spans="11:44">
       <c r="K48" t="s">
         <v>46</v>
       </c>
       <c r="L48" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="11:12">
@@ -6779,7 +6818,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1205EC6D-6A64-4D12-BC62-CF236498DB53}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00A3AF06-D328-4A9D-870F-54735B4D42F2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>

--- a/lab1/lab1.xlsx
+++ b/lab1/lab1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="11320"/>
+    <workbookView windowWidth="28800" windowHeight="13560"/>
   </bookViews>
   <sheets>
     <sheet name="Новый текстовый документ" sheetId="2" r:id="rId1"/>
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="X">'Новый текстовый документ'!$A$2:$J$11</definedName>
+    <definedName name="n">'Новый текстовый документ'!$A$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -247,13 +248,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="176" formatCode="_-* #\ ##0.00_-;\-* #\ ##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #\ ##0.00\ &quot;₽&quot;_-;\-* #\ ##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-* #\ ##0_-;\-* #\ ##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\ ##0\ &quot;₽&quot;_-;\-* #\ ##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="0.0000"/>
     <numFmt numFmtId="181" formatCode="0.00000000"/>
+    <numFmt numFmtId="182" formatCode="0.000"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -894,7 +896,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -934,6 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5067,7 +5070,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4862195" y="3302000"/>
-        <a:ext cx="5321300" cy="4155440"/>
+        <a:ext cx="5534660" cy="4155440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5096,7 +5099,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10197465" y="3340100"/>
+        <a:off x="10410825" y="3340100"/>
         <a:ext cx="4015105" cy="4155440"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5127,7 +5130,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6117590" y="7642225"/>
-        <a:ext cx="4460875" cy="3063240"/>
+        <a:ext cx="4674235" cy="3063240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5157,7 +5160,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6268085" y="11227435"/>
-        <a:ext cx="4310380" cy="3086100"/>
+        <a:ext cx="4523740" cy="3086100"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5432,6 +5435,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="10" width="5" customWidth="1"/>
+    <col min="16" max="16" width="11.625"/>
     <col min="17" max="17" width="14.2890625" customWidth="1"/>
     <col min="18" max="18" width="2.140625" customWidth="1"/>
     <col min="19" max="20" width="4.859375" customWidth="1"/>
@@ -5624,8 +5628,8 @@
         <v>0.108583937137685</v>
       </c>
       <c r="P3">
-        <f>1+LOG(100,2)</f>
-        <v>7.64385618977473</v>
+        <f>1+LOG(n,2)</f>
+        <v>7.64385618977472</v>
       </c>
       <c r="Q3">
         <f>ROUNDUP(O3,2)</f>
@@ -5654,11 +5658,11 @@
         <v>2</v>
       </c>
       <c r="X3">
-        <f>V3/100</f>
+        <f>V3/n</f>
         <v>0.02</v>
       </c>
       <c r="Y3">
-        <f>W3/100</f>
+        <f>W3/n</f>
         <v>0.02</v>
       </c>
       <c r="Z3" s="8">
@@ -5725,11 +5729,11 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <f t="shared" ref="X4:X10" si="3">V4/100</f>
+        <f>V4/n</f>
         <v>0.03</v>
       </c>
       <c r="Y4">
-        <f t="shared" ref="Y4:Y10" si="4">W4/100</f>
+        <f>W4/n</f>
         <v>0.05</v>
       </c>
       <c r="Z4" s="8">
@@ -5788,15 +5792,15 @@
         <v>12</v>
       </c>
       <c r="W5">
-        <f t="shared" ref="W5:W10" si="5">W4+V5</f>
+        <f t="shared" ref="W5:W10" si="3">W4+V5</f>
         <v>17</v>
       </c>
       <c r="X5">
-        <f t="shared" si="3"/>
+        <f>V5/n</f>
         <v>0.12</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="4"/>
+        <f>W5/n</f>
         <v>0.17</v>
       </c>
       <c r="Z5" s="8">
@@ -5855,15 +5859,15 @@
         <v>19</v>
       </c>
       <c r="W6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="X6">
-        <f t="shared" si="3"/>
+        <f>V6/n</f>
         <v>0.19</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="4"/>
+        <f>W6/n</f>
         <v>0.36</v>
       </c>
       <c r="Z6" s="8">
@@ -5922,15 +5926,15 @@
         <v>29</v>
       </c>
       <c r="W7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="X7">
-        <f t="shared" si="3"/>
+        <f>V7/n</f>
         <v>0.29</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="4"/>
+        <f>W7/n</f>
         <v>0.65</v>
       </c>
       <c r="Z7" s="8">
@@ -5989,15 +5993,15 @@
         <v>18</v>
       </c>
       <c r="W8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>83</v>
       </c>
       <c r="X8">
-        <f t="shared" si="3"/>
+        <f>V8/n</f>
         <v>0.18</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="4"/>
+        <f>W8/n</f>
         <v>0.83</v>
       </c>
       <c r="Z8" s="8">
@@ -6056,15 +6060,15 @@
         <v>12</v>
       </c>
       <c r="W9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>95</v>
       </c>
       <c r="X9">
-        <f t="shared" si="3"/>
+        <f>V9/n</f>
         <v>0.12</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="4"/>
+        <f>W9/n</f>
         <v>0.95</v>
       </c>
       <c r="Z9" s="8">
@@ -6123,15 +6127,15 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="X10">
-        <f t="shared" si="3"/>
+        <f>V10/n</f>
         <v>0.05</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="4"/>
+        <f>W10/n</f>
         <v>1</v>
       </c>
       <c r="Z10" s="8">
@@ -6169,6 +6173,12 @@
       </c>
       <c r="J11" s="6">
         <v>5.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13">
+        <f>COUNT(X)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="11:47">
@@ -6237,7 +6247,7 @@
     </row>
     <row r="21" spans="11:47">
       <c r="K21" t="str">
-        <f t="shared" ref="K21:K28" si="6">TEXT(S3,"0,00")&amp;"–"&amp;TEXT(T3,"0,00")</f>
+        <f t="shared" ref="K21:K28" si="4">TEXT(S3,"0,00")&amp;"–"&amp;TEXT(T3,"0,00")</f>
         <v>4,98–5,09</v>
       </c>
       <c r="AB21" s="10" t="s">
@@ -6266,21 +6276,23 @@
     </row>
     <row r="22" spans="11:47">
       <c r="K22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5,09–5,20</v>
       </c>
       <c r="AB22" t="s">
         <v>26</v>
       </c>
       <c r="AC22">
+        <f>SUM(X)/n</f>
         <v>5.4493</v>
       </c>
       <c r="AD22">
         <f>AVERAGE(X)</f>
         <v>5.4493</v>
       </c>
-      <c r="AE22">
-        <v>4.4717</v>
+      <c r="AE22" cm="1">
+        <f t="array" ref="AE22">SUMPRODUCT(U3:U10,V3:V10)/n</f>
+        <v>5.4717</v>
       </c>
       <c r="AH22" t="s">
         <v>27</v>
@@ -6311,21 +6323,23 @@
     </row>
     <row r="23" ht="34" spans="11:47">
       <c r="K23" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5,20–5,31</v>
       </c>
       <c r="AB23" t="s">
         <v>29</v>
       </c>
-      <c r="AC23">
-        <v>5.4441</v>
+      <c r="AC23" s="13" cm="1">
+        <f t="array" ref="AC23">n/SUMPRODUCT(1/X)</f>
+        <v>5.44410601929593</v>
       </c>
       <c r="AD23" s="13">
         <f>HARMEAN(X)</f>
         <v>5.44410601929593</v>
       </c>
-      <c r="AE23">
-        <v>5.4664</v>
+      <c r="AE23" s="13" cm="1">
+        <f t="array" ref="AE23">n/SUMPRODUCT(V3:V10,1/U3:U10)</f>
+        <v>5.46642788905488</v>
       </c>
       <c r="AH23" t="s">
         <v>30</v>
@@ -6353,21 +6367,23 @@
     </row>
     <row r="24" spans="11:47">
       <c r="K24" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5,31–5,42</v>
       </c>
       <c r="AB24" t="s">
         <v>32</v>
       </c>
-      <c r="AC24">
-        <v>5.4467</v>
+      <c r="AC24" s="13">
+        <f>(PRODUCT(X)^(1/n))</f>
+        <v>5.44670600437583</v>
       </c>
       <c r="AD24" s="13">
         <f>GEOMEAN(X)</f>
         <v>5.44670600437583</v>
       </c>
-      <c r="AE24">
-        <v>5.4691</v>
+      <c r="AE24" s="13" cm="1">
+        <f t="array" ref="AE24">PRODUCT(U3:U10^V3:V10)^(1/n)</f>
+        <v>5.46906961756163</v>
       </c>
       <c r="AH24" t="s">
         <v>33</v>
@@ -6395,13 +6411,14 @@
     </row>
     <row r="25" ht="34" spans="11:47">
       <c r="K25" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5,42–5,53</v>
       </c>
       <c r="AB25" t="s">
         <v>35</v>
       </c>
       <c r="AC25">
+        <f>(SMALL(X,50)+SMALL(X,51))/2</f>
         <v>5.43</v>
       </c>
       <c r="AD25">
@@ -6437,7 +6454,7 @@
     </row>
     <row r="26" ht="34" spans="11:47">
       <c r="K26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5,53–5,64</v>
       </c>
       <c r="AB26" t="s">
@@ -6479,7 +6496,7 @@
     </row>
     <row r="27" ht="34" spans="11:47">
       <c r="K27" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5,64–5,75</v>
       </c>
       <c r="AH27" t="s">
@@ -6508,7 +6525,7 @@
     </row>
     <row r="28" ht="30" customHeight="1" spans="11:47">
       <c r="K28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5,75–5,86</v>
       </c>
       <c r="AM28" s="18" t="s">
@@ -6587,7 +6604,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="11:44">
+    <row r="33" spans="11:47">
       <c r="K33">
         <f>U3</f>
         <v>5.035</v>
@@ -6599,87 +6616,127 @@
       <c r="AR33" t="s">
         <v>52</v>
       </c>
+      <c r="AS33" s="13">
+        <f>AN29</f>
+        <v>-0.0428940019139835</v>
+      </c>
+      <c r="AT33" s="13">
+        <f>AP29</f>
+        <v>-0.147197420844705</v>
+      </c>
+      <c r="AU33" s="19">
+        <f>SQRT(6*(n-1)/((n+1)*(n+3)))</f>
+        <v>0.238953790040821</v>
+      </c>
     </row>
-    <row r="34" spans="11:44">
+    <row r="34" spans="11:47">
       <c r="K34">
-        <f t="shared" ref="K34:L34" si="7">U4</f>
+        <f t="shared" ref="K34:L34" si="5">U4</f>
         <v>5.145</v>
       </c>
       <c r="L34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AR34" t="s">
         <v>53</v>
       </c>
+      <c r="AS34" s="8">
+        <f>ABS(AS33)/AU33</f>
+        <v>0.179507518615444</v>
+      </c>
+      <c r="AT34" s="8">
+        <f>ABS(AT33)/AU33</f>
+        <v>0.616007893490869</v>
+      </c>
     </row>
-    <row r="35" spans="11:44">
+    <row r="35" spans="11:47">
       <c r="K35">
-        <f t="shared" ref="K35:L35" si="8">U5</f>
+        <f t="shared" ref="K35:L35" si="6">U5</f>
         <v>5.255</v>
       </c>
       <c r="L35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="AR35" t="s">
         <v>54</v>
       </c>
+      <c r="AS35" s="13">
+        <f>AN30</f>
+        <v>-0.0168593707522868</v>
+      </c>
+      <c r="AT35" s="13">
+        <f>AO30</f>
+        <v>0.0447531192770798</v>
+      </c>
+      <c r="AU35">
+        <f>SQRT(24*n*(n-2)*(n-3)/((n-1)^2*(n+3)*(n+5)))</f>
+        <v>0.463933858815294</v>
+      </c>
     </row>
-    <row r="36" spans="11:44">
+    <row r="36" spans="11:47">
       <c r="K36">
-        <f t="shared" ref="K36:L36" si="9">U6</f>
+        <f t="shared" ref="K36:L36" si="7">U6</f>
         <v>5.365</v>
       </c>
       <c r="L36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="AR36" t="s">
         <v>55</v>
       </c>
+      <c r="AS36" s="13">
+        <f>ABS(AS35)/AU35</f>
+        <v>0.0363400308728038</v>
+      </c>
+      <c r="AT36" s="13">
+        <f>ABS(AT35)/AU35</f>
+        <v>0.0964644386839146</v>
+      </c>
     </row>
-    <row r="37" spans="11:44">
+    <row r="37" spans="11:47">
       <c r="K37">
-        <f t="shared" ref="K37:L37" si="10">U7</f>
+        <f t="shared" ref="K37:L37" si="8">U7</f>
         <v>5.475</v>
       </c>
       <c r="L37">
+        <f t="shared" si="8"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="11:47">
+      <c r="K38">
+        <f t="shared" ref="K38:L38" si="9">U8</f>
+        <v>5.585</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="11:47">
+      <c r="K39">
+        <f t="shared" ref="K39:L39" si="10">U9</f>
+        <v>5.695</v>
+      </c>
+      <c r="L39">
         <f t="shared" si="10"/>
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="38" spans="11:44">
-      <c r="K38">
-        <f t="shared" ref="K38:L38" si="11">U8</f>
-        <v>5.585</v>
-      </c>
-      <c r="L38">
+    <row r="40" spans="11:47">
+      <c r="K40">
+        <f t="shared" ref="K40:L40" si="11">U10</f>
+        <v>5.805</v>
+      </c>
+      <c r="L40">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="39" spans="11:44">
-      <c r="K39">
-        <f t="shared" ref="K39:L39" si="12">U9</f>
-        <v>5.695</v>
-      </c>
-      <c r="L39">
-        <f t="shared" si="12"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="11:44">
-      <c r="K40">
-        <f t="shared" ref="K40:L40" si="13">U10</f>
-        <v>5.805</v>
-      </c>
-      <c r="L40">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="11:44">
+    <row r="41" spans="11:47">
       <c r="K41">
         <f>U10+Q3</f>
         <v>5.915</v>
@@ -6688,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="11:44">
+    <row r="48" spans="11:47">
       <c r="K48" t="s">
         <v>46</v>
       </c>
@@ -6717,71 +6774,71 @@
     </row>
     <row r="51" spans="11:12">
       <c r="K51" s="8">
-        <f t="shared" ref="K51:K57" si="14">T4</f>
+        <f t="shared" ref="K51:K57" si="12">T4</f>
         <v>5.2</v>
       </c>
       <c r="L51">
-        <f t="shared" ref="L51:L57" si="15">Y4</f>
+        <f t="shared" ref="L51:L57" si="13">Y4</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="52" spans="11:12">
       <c r="K52" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>5.31</v>
       </c>
       <c r="L52">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="53" spans="11:12">
       <c r="K53" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>5.42</v>
       </c>
       <c r="L53">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.36</v>
       </c>
     </row>
     <row r="54" spans="11:12">
       <c r="K54" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>5.53</v>
       </c>
       <c r="L54">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.65</v>
       </c>
     </row>
     <row r="55" spans="11:12">
       <c r="K55" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>5.64</v>
       </c>
       <c r="L55">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.83</v>
       </c>
     </row>
     <row r="56" spans="11:12">
       <c r="K56" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>5.75</v>
       </c>
       <c r="L56">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="11:12">
       <c r="K57" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>5.86</v>
       </c>
       <c r="L57">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -6818,7 +6875,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00A3AF06-D328-4A9D-870F-54735B4D42F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D355E50-2AD1-4F1F-8FA7-C66613319466}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>

--- a/lab1/lab1.xlsx
+++ b/lab1/lab1.xlsx
@@ -6485,8 +6485,8 @@
         <v>40</v>
       </c>
       <c r="AN26" s="12">
-        <f>AI26</f>
-        <v>-0.000203263385999937</v>
+        <f>AI25</f>
+        <v>0.02821251</v>
       </c>
       <c r="AO26" s="12"/>
       <c r="AP26" s="12">
@@ -6514,8 +6514,8 @@
         <v>42</v>
       </c>
       <c r="AN27" s="12">
-        <f>AI27</f>
-        <v>0.0023744180174997</v>
+        <f>AI26</f>
+        <v>-0.000203263385999937</v>
       </c>
       <c r="AO27" s="12"/>
       <c r="AP27" s="12">
@@ -6667,8 +6667,8 @@
         <v>-0.0168593707522868</v>
       </c>
       <c r="AT35" s="13">
-        <f>AO30</f>
-        <v>0.0447531192770798</v>
+        <f>AP30</f>
+        <v>-0.196896626523966</v>
       </c>
       <c r="AU35">
         <f>SQRT(24*n*(n-2)*(n-3)/((n-1)^2*(n+3)*(n+5)))</f>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="AT36" s="13">
         <f>ABS(AT35)/AU35</f>
-        <v>0.0964644386839146</v>
+        <v>0.4244066751815941</v>
       </c>
     </row>
     <row r="37" spans="11:47">

--- a/lab1/lab1.xlsx
+++ b/lab1/lab1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13560"/>
+    <workbookView windowWidth="27660" windowHeight="13560"/>
   </bookViews>
   <sheets>
     <sheet name="Новый текстовый документ" sheetId="2" r:id="rId1"/>
@@ -2460,8 +2460,9 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -2478,69 +2479,115 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700" cmpd="sng">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:round/>
+              <a:prstDash val="solid"/>
             </a:ln>
             <a:effectLst/>
+            <a:sp3d contourW="12700"/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>'Новый текстовый документ'!$K$49:$K$57</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
-                <c:pt idx="0">
+                <c:pt idx="0" c:formatCode="0.00">
                   <c:v>4.98</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="1" c:formatCode="0.00">
                   <c:v>5.09</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="2" c:formatCode="0.00">
                   <c:v>5.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="3" c:formatCode="0.00">
                   <c:v>5.31</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="4" c:formatCode="0.00">
                   <c:v>5.42</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="5" c:formatCode="0.00">
                   <c:v>5.53</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="6" c:formatCode="0.00">
                   <c:v>5.64</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="7" c:formatCode="0.00">
                   <c:v>5.75</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="8" c:formatCode="0.00">
                   <c:v>5.86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'Новый текстовый документ'!$L$49:$L$57</c:f>
               <c:numCache>
@@ -2575,7 +2622,114 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:overlap val="0"/>
+        <c:axId val="903039855"/>
+        <c:axId val="749613967"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Новый текстовый документ'!$K$49:$K$57</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0" c:formatCode="0.00">
+                  <c:v>4.98</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="0.00">
+                  <c:v>5.09</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="0.00">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="0.00">
+                  <c:v>5.31</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="0.00">
+                  <c:v>5.42</c:v>
+                </c:pt>
+                <c:pt idx="5" c:formatCode="0.00">
+                  <c:v>5.53</c:v>
+                </c:pt>
+                <c:pt idx="6" c:formatCode="0.00">
+                  <c:v>5.64</c:v>
+                </c:pt>
+                <c:pt idx="7" c:formatCode="0.00">
+                  <c:v>5.75</c:v>
+                </c:pt>
+                <c:pt idx="8" c:formatCode="0.00">
+                  <c:v>5.86</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Новый текстовый документ'!$L$49:$L$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
           <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
@@ -2586,14 +2740,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="903039855"/>
-        <c:axId val="749613967"/>
-      </c:scatterChart>
-      <c:valAx>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="799063452"/>
+        <c:axId val="783128877"/>
+      </c:lineChart>
+      <c:catAx>
         <c:axId val="903039855"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="4.98"/>
+          <c:min val="0.5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2614,7 +2770,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -2641,14 +2797,6 @@
                   </a:rPr>
                   <a:t>Объём основных фондов, млн руб.</a:t>
                 </a:r>
-                <a:endParaRPr lang="ru-RU" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:sysClr>
-                  </a:solidFill>
-                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2680,7 +2828,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -2700,9 +2848,11 @@
         </c:txPr>
         <c:crossAx val="749613967"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.11"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="749613967"/>
         <c:scaling>
@@ -2799,7 +2949,90 @@
         </c:txPr>
         <c:crossAx val="903039855"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="799063452"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="783128877"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="783128877"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="799063452"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -5142,16 +5375,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>720090</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:rowOff>16510</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
+      <xdr:colOff>374015</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>115570</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5159,7 +5392,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6268085" y="11227435"/>
+        <a:off x="6247130" y="11068050"/>
         <a:ext cx="4523740" cy="3086100"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6359,7 +6592,10 @@
         <f>SQRT(AN22)</f>
         <v>0.167965800090376</v>
       </c>
-      <c r="AO23" s="12"/>
+      <c r="AO23" s="12">
+        <f>_xlfn.STDEV.S(X)</f>
+        <v>0.168811980761097</v>
+      </c>
       <c r="AP23" s="12">
         <f>SQRT(AP22)</f>
         <v>0.169310690743379</v>
@@ -6693,7 +6929,7 @@
       </c>
       <c r="AT36" s="13">
         <f>ABS(AT35)/AU35</f>
-        <v>0.4244066751815941</v>
+        <v>0.424406675181594</v>
       </c>
     </row>
     <row r="37" spans="11:47">
@@ -6875,7 +7111,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D355E50-2AD1-4F1F-8FA7-C66613319466}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6E5E5A4-69CD-4192-994D-4BEB4BE68167}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>
